--- a/光伏配储项目/电价数据/2026/林益站.xlsx
+++ b/光伏配储项目/电价数据/2026/林益站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5085</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74242</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57163</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5800700000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42284</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09423999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10254</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08648</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07856999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09186</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09465999999999999</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06408</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03227</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.03057</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14197</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21104</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01188</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24297</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24033</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17827</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.71761</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.60127</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57089</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60412</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79037</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6414800000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.60521</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7339199999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.8694700000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6613300000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58617</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6637799999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6231599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60002</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47029</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6884199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15991</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6705599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.73751</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7081900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5176499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.57069</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15414</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06422</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47571</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7428899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.95394</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.67114</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.15599</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22746</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.23736</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.59774</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66783</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6570199999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71363</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75471</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.56857</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50798</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20281</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22338</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.20441</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19234</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16972</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48058</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5568099999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49242</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17066</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48589</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5148400000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59856</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54323</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.60489</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47113</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43888</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44512</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14795</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16918</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26435</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56664</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07003</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06967</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.08992</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20795</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.65116</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.17551</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45826</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.48286</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.52327</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29941</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04836</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04831000000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.06545000000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02673</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.02318</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02688</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01667</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.02177</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02493</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02576</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.01363</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03672</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04196</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.01775</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03627</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03917</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03847</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.01851</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21932</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.06598999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.07499</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00395</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15226</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02877</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09176000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35138</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65544</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.01932</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03483</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.01225</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.009699999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03836</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03625</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02511</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02719</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33562</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31712</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9138999999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8620599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29571</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88663</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6314299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18623</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86833</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54423</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.32998</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03231</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5299199999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79026</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77224</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77696</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87348</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49247</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2061</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62097</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5380900000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58774</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59648</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60341</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69528</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46786</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58226</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8847699999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84417</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82363</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44212</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45415</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35381</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91912</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46743</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50232</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16404</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19344</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.6004299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8913300000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35976</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16626</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7011900000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79222</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58574</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45404</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45151</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50198</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49581</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54206</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11585</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57148</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32463</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22043</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13692</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15049</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14173</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13484</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14073</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13351</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13371</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25337</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09124</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10503</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10524</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11592</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13231</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13662</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45603</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34936</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54139</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19456</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24777</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36087</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42716</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08874</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6890299999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29153</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.49497</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35003</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7778400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21435</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6881699999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6436799999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65613</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.54073</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.88418</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49491</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.87109</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.51701</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50119</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3607</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52955</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48682</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50527</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49025</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44765</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.18712</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49486</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.2741</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.59239</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.74178</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.76381</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.04361</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.14505</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81374</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58635</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83839</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76888</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6716799999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44064</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47891</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47131</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5544199999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18706</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46244</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10748</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18282</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36799</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22928</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22839</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24795</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16686</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18562</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23307</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23662</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22702</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.007719999999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15763</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03167</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04196</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03012</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02863</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01319</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03413</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21528</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48646</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40646</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9933200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9722499999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47878</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48882</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5665800000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46836</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.00364</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.0763</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.94435</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.98753</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18803</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.19071</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08505</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32396</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25113</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49531</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52123</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14047</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27429</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47205</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5741900000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45897</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36877</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56228</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.56736</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.62619</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5222899999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.56087</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73719</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70111</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53327</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5332899999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37294</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40392</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05833</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13364</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02612</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20289</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15488</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00756</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14677</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05739</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06659000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18234</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07171999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.22013</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48546</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38785</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06927</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5765</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5223099999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.02049</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01955</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02689</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00612</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00276</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15605</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18844</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37025</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18598</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15536</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21277</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12286</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.22954</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04701</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04388</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10313</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.08087000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13419</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24357</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16486</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16897</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05449</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21386</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15386</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26435</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39801</v>
       </c>
     </row>
   </sheetData>
